--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1030,6 +1030,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1039,7 +1042,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1353,6 +1356,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1396,7 +1402,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1711,6 +1717,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,7 +1729,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2031,6 +2040,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2074,7 +2086,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2389,6 +2401,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2398,7 +2413,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2712,6 +2727,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2734,11 +2752,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433547904"/>
-        <c:axId val="466712448"/>
+        <c:axId val="154698496"/>
+        <c:axId val="154700416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433547904"/>
+        <c:axId val="154698496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2781,14 +2799,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466712448"/>
+        <c:crossAx val="154700416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466712448"/>
+        <c:axId val="154700416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2837,7 +2855,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433547904"/>
+        <c:crossAx val="154698496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3034,7 +3052,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3313,6 +3331,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3322,7 +3343,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3600,6 +3621,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3643,7 +3667,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3922,6 +3946,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3931,7 +3958,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4209,6 +4236,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4252,7 +4282,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4531,6 +4561,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4540,7 +4573,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4818,6 +4851,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4840,11 +4876,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="487244544"/>
-        <c:axId val="487246464"/>
+        <c:axId val="595686528"/>
+        <c:axId val="595688832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="487244544"/>
+        <c:axId val="595686528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4887,14 +4923,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487246464"/>
+        <c:crossAx val="595688832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="487246464"/>
+        <c:axId val="595688832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4943,7 +4979,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487244544"/>
+        <c:crossAx val="595686528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5140,7 +5176,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5419,6 +5455,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5428,7 +5467,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5706,6 +5745,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5749,7 +5791,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6028,6 +6070,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6037,7 +6082,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6315,6 +6360,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6358,7 +6406,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6637,6 +6685,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6646,7 +6697,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6924,6 +6975,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -6946,11 +7000,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="533718528"/>
-        <c:axId val="533720064"/>
+        <c:axId val="528072064"/>
+        <c:axId val="528077952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533718528"/>
+        <c:axId val="528072064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6993,14 +7047,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533720064"/>
+        <c:crossAx val="528077952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533720064"/>
+        <c:axId val="528077952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7049,7 +7103,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533718528"/>
+        <c:crossAx val="528072064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7556,7 +7610,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12003,7 +12057,7 @@
         <v>1.87002</v>
       </c>
       <c r="C108" s="20">
-        <v>1.1261140396413394</v>
+        <v>1.1257628092540124</v>
       </c>
       <c r="D108" s="21">
         <v>0</v>
@@ -12027,6 +12081,41 @@
         <v>259.19582720385745</v>
       </c>
       <c r="K108" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B109" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.1334752732368041</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I109" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J109" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K109" s="21">
         <v>795.53573587245569</v>
       </c>
     </row>
@@ -12048,7 +12137,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -15953,7 +16042,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -15977,6 +16066,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K96" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I97" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J97" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K97" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -15998,7 +16122,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -19903,7 +20027,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -19927,6 +20051,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K96" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I97" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J97" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K97" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1033,6 +1033,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,7 +1045,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1359,6 +1362,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1402,7 +1408,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1720,6 +1726,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1729,7 +1738,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2043,6 +2052,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2086,7 +2098,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2404,6 +2416,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2413,7 +2428,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2730,6 +2745,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2752,11 +2770,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="154698496"/>
-        <c:axId val="154700416"/>
+        <c:axId val="493124992"/>
+        <c:axId val="493799680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="154698496"/>
+        <c:axId val="493124992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2799,14 +2817,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154700416"/>
+        <c:crossAx val="493799680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="154700416"/>
+        <c:axId val="493799680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2855,7 +2873,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154698496"/>
+        <c:crossAx val="493124992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3052,7 +3070,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3334,6 +3352,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3343,7 +3364,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3624,6 +3645,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3667,7 +3691,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3949,6 +3973,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3958,7 +3985,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4239,6 +4266,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4282,7 +4312,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4564,6 +4594,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4573,7 +4606,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4854,6 +4887,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4876,11 +4912,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595686528"/>
-        <c:axId val="595688832"/>
+        <c:axId val="559792512"/>
+        <c:axId val="559794816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595686528"/>
+        <c:axId val="559792512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4923,14 +4959,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595688832"/>
+        <c:crossAx val="559794816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595688832"/>
+        <c:axId val="559794816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4979,7 +5015,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595686528"/>
+        <c:crossAx val="559792512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5176,7 +5212,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5458,6 +5494,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5467,7 +5506,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5748,6 +5787,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5791,7 +5833,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6073,6 +6115,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6082,7 +6127,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6363,6 +6408,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6406,7 +6454,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6688,6 +6736,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6697,7 +6748,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6978,6 +7029,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7000,11 +7054,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528072064"/>
-        <c:axId val="528077952"/>
+        <c:axId val="89639936"/>
+        <c:axId val="89649920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528072064"/>
+        <c:axId val="89639936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7047,14 +7101,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528077952"/>
+        <c:crossAx val="89649920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528077952"/>
+        <c:axId val="89649920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7103,7 +7157,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528072064"/>
+        <c:crossAx val="89639936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7211,7 +7265,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7254,7 +7308,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7297,7 +7351,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7610,7 +7664,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12119,6 +12173,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.1419948172142516</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I110" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J110" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K110" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12137,7 +12226,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16104,6 +16193,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I98" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J98" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K98" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16122,7 +16246,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20089,6 +20213,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I98" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J98" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K98" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1036,6 +1036,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1045,7 +1048,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1365,6 +1368,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1408,7 +1414,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1729,6 +1735,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1738,7 +1747,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2055,6 +2064,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2098,7 +2110,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2419,6 +2431,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2428,7 +2443,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2748,6 +2763,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2770,11 +2788,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="493124992"/>
-        <c:axId val="493799680"/>
+        <c:axId val="77543296"/>
+        <c:axId val="77544832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="493124992"/>
+        <c:axId val="77543296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2817,14 +2835,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493799680"/>
+        <c:crossAx val="77544832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493799680"/>
+        <c:axId val="77544832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2873,7 +2891,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493124992"/>
+        <c:crossAx val="77543296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3070,7 +3088,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3355,6 +3373,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3364,7 +3385,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3648,6 +3669,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3691,7 +3715,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3976,6 +4000,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3985,7 +4012,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4269,6 +4296,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4312,7 +4342,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4597,6 +4627,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4606,7 +4639,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4890,6 +4923,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4912,11 +4948,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559792512"/>
-        <c:axId val="559794816"/>
+        <c:axId val="436425088"/>
+        <c:axId val="436426624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559792512"/>
+        <c:axId val="436425088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4959,14 +4995,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559794816"/>
+        <c:crossAx val="436426624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559794816"/>
+        <c:axId val="436426624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5015,7 +5051,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559792512"/>
+        <c:crossAx val="436425088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5212,7 +5248,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5497,6 +5533,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5506,7 +5545,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5790,6 +5829,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5833,7 +5875,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6118,6 +6160,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6127,7 +6172,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6411,6 +6456,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6454,7 +6502,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6739,6 +6787,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6748,7 +6799,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7032,6 +7083,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7054,11 +7108,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="89639936"/>
-        <c:axId val="89649920"/>
+        <c:axId val="483410304"/>
+        <c:axId val="483411840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="89639936"/>
+        <c:axId val="483410304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7101,14 +7155,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89649920"/>
+        <c:crossAx val="483411840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="89649920"/>
+        <c:axId val="483411840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7157,7 +7211,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89639936"/>
+        <c:crossAx val="483410304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7265,7 +7319,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7308,7 +7362,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7351,7 +7405,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7664,7 +7718,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12208,6 +12262,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.1482512499999991</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I111" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J111" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K111" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12226,7 +12315,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16228,6 +16317,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I99" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J99" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K99" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16246,7 +16370,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20248,6 +20372,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I99" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J99" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K99" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1039,6 +1039,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1048,7 +1051,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1371,6 +1374,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1414,7 +1420,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1738,6 +1744,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1747,7 +1756,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2067,6 +2076,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2110,7 +2122,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2434,6 +2446,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2443,7 +2458,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2766,6 +2781,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2788,11 +2806,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="77543296"/>
-        <c:axId val="77544832"/>
+        <c:axId val="393924992"/>
+        <c:axId val="394999680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="77543296"/>
+        <c:axId val="393924992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,14 +2853,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77544832"/>
+        <c:crossAx val="394999680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="77544832"/>
+        <c:axId val="394999680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2891,7 +2909,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77543296"/>
+        <c:crossAx val="393924992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3088,7 +3106,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3376,6 +3394,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3385,7 +3406,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3672,6 +3693,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3715,7 +3739,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4003,6 +4027,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4012,7 +4039,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4299,6 +4326,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4342,7 +4372,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4630,6 +4660,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4639,7 +4672,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4926,6 +4959,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4948,11 +4984,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="436425088"/>
-        <c:axId val="436426624"/>
+        <c:axId val="442077184"/>
+        <c:axId val="442078720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="436425088"/>
+        <c:axId val="442077184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4995,14 +5031,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436426624"/>
+        <c:crossAx val="442078720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="436426624"/>
+        <c:axId val="442078720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5051,7 +5087,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436425088"/>
+        <c:crossAx val="442077184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5248,7 +5284,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5536,6 +5572,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5545,7 +5584,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5832,6 +5871,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5875,7 +5917,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6163,6 +6205,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6172,7 +6217,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6459,6 +6504,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6502,7 +6550,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6790,6 +6838,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6799,7 +6850,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7086,6 +7137,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7108,11 +7162,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483410304"/>
-        <c:axId val="483411840"/>
+        <c:axId val="160742400"/>
+        <c:axId val="160748288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483410304"/>
+        <c:axId val="160742400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7155,14 +7209,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483411840"/>
+        <c:crossAx val="160748288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483411840"/>
+        <c:axId val="160748288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7211,7 +7265,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483410304"/>
+        <c:crossAx val="160742400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7319,7 +7373,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7362,7 +7416,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7405,7 +7459,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7718,7 +7772,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12297,6 +12351,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B112" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.1561043221110083</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I112" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J112" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K112" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12315,7 +12404,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16352,6 +16441,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I100" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J100" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K100" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16370,7 +16494,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20407,6 +20531,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I100" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J100" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K100" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1042,6 +1042,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1051,7 +1054,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1377,6 +1380,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1420,7 +1426,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1747,6 +1753,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1756,7 +1765,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2079,6 +2088,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2122,7 +2134,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2449,6 +2461,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,7 +2473,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2784,6 +2799,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2806,11 +2824,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="393924992"/>
-        <c:axId val="394999680"/>
+        <c:axId val="401424384"/>
+        <c:axId val="401426304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="393924992"/>
+        <c:axId val="401424384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2853,14 +2871,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="394999680"/>
+        <c:crossAx val="401426304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="394999680"/>
+        <c:axId val="401426304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2909,7 +2927,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393924992"/>
+        <c:crossAx val="401424384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3106,7 +3124,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3397,6 +3415,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3406,7 +3427,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3696,6 +3717,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3739,7 +3763,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4030,6 +4054,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4039,7 +4066,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4329,6 +4356,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4372,7 +4402,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4663,6 +4693,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4672,7 +4705,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4962,6 +4995,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4984,11 +5020,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442077184"/>
-        <c:axId val="442078720"/>
+        <c:axId val="472211456"/>
+        <c:axId val="472213376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442077184"/>
+        <c:axId val="472211456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5031,14 +5067,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442078720"/>
+        <c:crossAx val="472213376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442078720"/>
+        <c:axId val="472213376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5087,7 +5123,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442077184"/>
+        <c:crossAx val="472211456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5284,7 +5320,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5575,6 +5611,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5584,7 +5623,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5874,6 +5913,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5917,7 +5959,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6208,6 +6250,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6217,7 +6262,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6507,6 +6552,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6550,7 +6598,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6841,6 +6889,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6850,7 +6901,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7140,6 +7191,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7162,11 +7216,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="160742400"/>
-        <c:axId val="160748288"/>
+        <c:axId val="92112768"/>
+        <c:axId val="92114304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="160742400"/>
+        <c:axId val="92112768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7209,14 +7263,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160748288"/>
+        <c:crossAx val="92114304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160748288"/>
+        <c:axId val="92114304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7265,7 +7319,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160742400"/>
+        <c:crossAx val="92112768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7373,7 +7427,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7416,7 +7470,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7459,7 +7513,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7772,7 +7826,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12386,6 +12440,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B113" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.1626960820559045</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I113" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J113" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K113" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12404,7 +12493,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16476,6 +16565,41 @@
         <v>1725.4194238613065</v>
       </c>
     </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I101" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J101" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K101" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -16494,7 +16618,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20566,6 +20690,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I101" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J101" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K101" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4.xlsx
@@ -715,7 +715,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1045,6 +1045,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1054,7 +1057,7 @@
               <c:f>'model4(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1383,6 +1386,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1426,7 +1432,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1756,6 +1762,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1765,7 +1774,7 @@
               <c:f>'model4(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2091,6 +2100,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2134,7 +2146,7 @@
               <c:f>'model4(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2464,6 +2476,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2473,7 +2488,7 @@
               <c:f>'model4(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2802,6 +2817,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2824,11 +2842,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401424384"/>
-        <c:axId val="401426304"/>
+        <c:axId val="99720192"/>
+        <c:axId val="103724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401424384"/>
+        <c:axId val="99720192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2871,14 +2889,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401426304"/>
+        <c:crossAx val="103724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401426304"/>
+        <c:axId val="103724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2927,7 +2945,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401424384"/>
+        <c:crossAx val="99720192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3124,7 +3142,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3418,6 +3436,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3427,7 +3448,7 @@
               <c:f>'model4(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3721,6 +3742,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1179.7195080910908</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3763,7 +3787,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4057,6 +4081,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4066,7 +4093,7 @@
               <c:f>'model4(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4360,6 +4387,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1725.915575606366</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4402,7 +4432,7 @@
               <c:f>'model4(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4696,6 +4726,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4705,7 +4738,7 @@
               <c:f>'model4(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4998,6 +5031,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -5020,11 +5056,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472211456"/>
-        <c:axId val="472213376"/>
+        <c:axId val="399840384"/>
+        <c:axId val="399842304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472211456"/>
+        <c:axId val="399840384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5067,14 +5103,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472213376"/>
+        <c:crossAx val="399842304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472213376"/>
+        <c:axId val="399842304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5123,7 +5159,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472211456"/>
+        <c:crossAx val="399840384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5320,7 +5356,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5614,6 +5650,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5623,7 +5662,7 @@
               <c:f>'model4(3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5917,6 +5956,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>250.30355595263484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5959,7 +6001,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6253,6 +6295,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6262,7 +6307,7 @@
               <c:f>'model4(3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6556,6 +6601,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>380.48679167107468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6598,7 +6646,7 @@
               <c:f>'model4(3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6892,6 +6940,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6901,7 +6952,7 @@
               <c:f>'model4(3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7194,6 +7245,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7216,11 +7270,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92112768"/>
-        <c:axId val="92114304"/>
+        <c:axId val="442374784"/>
+        <c:axId val="448737664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92112768"/>
+        <c:axId val="442374784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7263,14 +7317,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92114304"/>
+        <c:crossAx val="448737664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92114304"/>
+        <c:axId val="448737664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7319,7 +7373,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92112768"/>
+        <c:crossAx val="442374784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7826,7 +7880,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12378,7 +12432,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C111" s="20">
-        <v>1.1482512499999991</v>
+        <v>1.1478195540229874</v>
       </c>
       <c r="D111" s="21">
         <v>0</v>
@@ -12413,7 +12467,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C112" s="20">
-        <v>1.1561043221110083</v>
+        <v>1.1556805234410541</v>
       </c>
       <c r="D112" s="21">
         <v>0</v>
@@ -12472,6 +12526,41 @@
         <v>259.19582720385745</v>
       </c>
       <c r="K113" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B114" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.1691162343470469</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I114" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J114" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K114" s="21">
         <v>795.53573587245569</v>
       </c>
     </row>
@@ -12490,10 +12579,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16503,7 +16590,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C99" s="20">
-        <v>1.7625963599999996</v>
+        <v>1.7605544399999997</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -16538,7 +16625,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C100" s="20">
-        <v>1.7862818</v>
+        <v>1.7846445999999998</v>
       </c>
       <c r="D100" s="21">
         <v>0</v>
@@ -16573,7 +16660,7 @@
         <v>1.9266700000000001</v>
       </c>
       <c r="C101" s="20">
-        <v>1.8123291999999998</v>
+        <v>1.8182105999999996</v>
       </c>
       <c r="D101" s="21">
         <v>0</v>
@@ -16597,6 +16684,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K101" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8510212799999999</v>
+      </c>
+      <c r="D102" s="21">
+        <v>0.49615174505950516</v>
+      </c>
+      <c r="E102" s="22">
+        <v>0.27065824303759423</v>
+      </c>
+      <c r="F102" s="22">
+        <v>0.27065824303759423</v>
+      </c>
+      <c r="G102" s="22">
+        <v>0.49615174505950516</v>
+      </c>
+      <c r="H102" s="22">
+        <v>1179.7195080910908</v>
+      </c>
+      <c r="I102" s="22">
+        <v>1725.915575606366</v>
+      </c>
+      <c r="J102" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K102" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16615,10 +16737,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20628,7 +20748,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C99" s="20">
-        <v>1.7625963599999996</v>
+        <v>1.7605544399999997</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -20663,7 +20783,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C100" s="20">
-        <v>1.7862818</v>
+        <v>1.7846445999999998</v>
       </c>
       <c r="D100" s="21">
         <v>0</v>
@@ -20698,7 +20818,7 @@
         <v>1.9266700000000001</v>
       </c>
       <c r="C101" s="20">
-        <v>1.8123291999999998</v>
+        <v>1.8182105999999996</v>
       </c>
       <c r="D101" s="21">
         <v>0</v>
@@ -20722,6 +20842,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K101" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8510212799999999</v>
+      </c>
+      <c r="D102" s="21">
+        <v>8.8767897933480899E-3</v>
+      </c>
+      <c r="E102" s="22">
+        <v>4.8424224104935765E-3</v>
+      </c>
+      <c r="F102" s="22">
+        <v>4.8424224104935765E-3</v>
+      </c>
+      <c r="G102" s="22">
+        <v>8.8767897933480899E-3</v>
+      </c>
+      <c r="H102" s="22">
+        <v>250.30355595263484</v>
+      </c>
+      <c r="I102" s="22">
+        <v>380.48679167107468</v>
+      </c>
+      <c r="J102" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K102" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>
